--- a/data/martyrs.xlsx
+++ b/data/martyrs.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P390"/>
+  <dimension ref="A1:P426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>data/frames\270_28.jpg;data/frames\270_30.jpg;data/frames\270_32.jpg</t>
+          <t>data/frames\270_25.jpg;data/frames\270_28.jpg;data/frames\270_30.jpg;data/frames\270_32.jpg;data/frames\270_35.jpg</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9484,7 +9484,11 @@
           <t>عمرو محمد ابو عوده</t>
         </is>
       </c>
-      <c r="D133" s="1" t="inlineStr"/>
+      <c r="D133" s="1" t="inlineStr">
+        <is>
+          <t>2002-03-05</t>
+        </is>
+      </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
           <t>10</t>
@@ -9512,7 +9516,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>data/frames\305_28.jpg;data/frames\305_30.jpg;data/frames\305_32.jpg</t>
+          <t>data/frames\305_25.jpg;data/frames\305_28.jpg;data/frames\305_30.jpg;data/frames\305_32.jpg;data/frames\305_35.jpg</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -9527,7 +9531,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>partial_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -10368,7 +10372,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>data/frames\332_28.jpg;data/frames\332_30.jpg;data/frames\332_32.jpg</t>
+          <t>data/frames\332_25.jpg;data/frames\332_28.jpg;data/frames\332_30.jpg;data/frames\332_32.jpg;data/frames\332_35.jpg</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -10574,7 +10578,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>data/frames\338_28.jpg;data/frames\338_30.jpg;data/frames\338_32.jpg</t>
+          <t>data/frames\338_25.jpg;data/frames\338_28.jpg;data/frames\338_30.jpg;data/frames\338_32.jpg;data/frames\338_35.jpg</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -10850,7 +10854,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>data/frames\346_28.jpg;data/frames\346_30.jpg;data/frames\346_32.jpg</t>
+          <t>data/frames\346_25.jpg;data/frames\346_28.jpg;data/frames\346_30.jpg;data/frames\346_32.jpg;data/frames\346_35.jpg</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -11853,7 +11857,7 @@
       <c r="E168" s="1" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>data/frames\380_28.jpg;data/frames\380_30.jpg;data/frames\380_32.jpg</t>
+          <t>data/frames\380_25.jpg;data/frames\380_28.jpg;data/frames\380_30.jpg;data/frames\380_32.jpg;data/frames\380_35.jpg</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -11885,7 +11889,7 @@
       <c r="E169" s="1" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>data/frames\386_28.jpg;data/frames\386_30.jpg;data/frames\386_32.jpg</t>
+          <t>data/frames\386_25.jpg;data/frames\386_28.jpg;data/frames\386_30.jpg;data/frames\386_32.jpg;data/frames\386_35.jpg</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -11917,7 +11921,7 @@
       <c r="E170" s="1" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>data/frames\710_28.jpg;data/frames\710_30.jpg;data/frames\710_32.jpg</t>
+          <t>data/frames\710_25.jpg;data/frames\710_28.jpg;data/frames\710_30.jpg;data/frames\710_32.jpg;data/frames\710_35.jpg</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -12333,7 +12337,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>data/frames\398_28.jpg;data/frames\398_30.jpg;data/frames\398_32.jpg</t>
+          <t>data/frames\398_25.jpg;data/frames\398_28.jpg;data/frames\398_30.jpg;data/frames\398_32.jpg;data/frames\398_35.jpg</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -13806,7 +13810,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>data/frames\449_28.jpg;data/frames\449_30.jpg;data/frames\449_32.jpg</t>
+          <t>data/frames\449_25.jpg;data/frames\449_28.jpg;data/frames\449_30.jpg;data/frames\449_32.jpg;data/frames\449_35.jpg</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -15977,7 +15981,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>data/frames\514_28.jpg;data/frames\514_30.jpg;data/frames\514_32.jpg</t>
+          <t>data/frames\514_25.jpg;data/frames\514_28.jpg;data/frames\514_30.jpg;data/frames\514_32.jpg;data/frames\514_35.jpg</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -19057,7 +19061,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>data/frames\606_28.jpg;data/frames\606_30.jpg;data/frames\606_32.jpg</t>
+          <t>data/frames\606_25.jpg;data/frames\606_28.jpg;data/frames\606_30.jpg;data/frames\606_32.jpg;data/frames\606_35.jpg</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -22541,12 +22545,21 @@
           <t>عمار كمال ابو سعاده</t>
         </is>
       </c>
-      <c r="D326" s="1" t="inlineStr"/>
+      <c r="D326" s="1" t="inlineStr">
+        <is>
+          <t>1993-11-03</t>
+        </is>
+      </c>
       <c r="E326" s="1" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>مجاهد _ قسامي</t>
+        </is>
+      </c>
       <c r="I326" t="inlineStr">
         <is>
           <t>كتيبة الصحابي أسد الله حمزة</t>
@@ -22562,6 +22575,11 @@
           <t>data/photos\712.jpg</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>data/frames\712_25.jpg;data/frames\712_28.jpg;data/frames\712_30.jpg;data/frames\712_32.jpg;data/frames\712_35.jpg</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>2026-05-02 07:06</t>
@@ -22574,7 +22592,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P326" t="inlineStr">
@@ -22597,12 +22615,21 @@
           <t>ماجد علي الاسطل</t>
         </is>
       </c>
-      <c r="D327" s="1" t="inlineStr"/>
+      <c r="D327" s="1" t="inlineStr">
+        <is>
+          <t>1995-12-01</t>
+        </is>
+      </c>
       <c r="E327" s="1" t="inlineStr">
         <is>
           <t>2023-10-23</t>
         </is>
       </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I327" t="inlineStr">
         <is>
           <t>كتيبة الصحابي أسامة بن زيد</t>
@@ -22618,6 +22645,11 @@
           <t>data/photos\714.jpg</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>data/frames\714_25.jpg;data/frames\714_28.jpg;data/frames\714_30.jpg;data/frames\714_32.jpg;data/frames\714_35.jpg</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>2026-05-02 09:01</t>
@@ -22630,7 +22662,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
@@ -22653,12 +22685,21 @@
           <t>بلال مازن العربيد</t>
         </is>
       </c>
-      <c r="D328" s="1" t="inlineStr"/>
+      <c r="D328" s="1" t="inlineStr">
+        <is>
+          <t>1986-11-15</t>
+        </is>
+      </c>
       <c r="E328" s="1" t="inlineStr">
         <is>
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I328" t="inlineStr">
         <is>
           <t>كتيبة الصحابي مصعب بن عمير</t>
@@ -22674,6 +22715,11 @@
           <t>data/photos\716.jpg</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>data/frames\716_25.jpg;data/frames\716_28.jpg;data/frames\716_30.jpg;data/frames\716_32.jpg;data/frames\716_35.jpg</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>2026-05-02 11:05</t>
@@ -22686,7 +22732,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
@@ -22715,6 +22761,11 @@
           <t>2023-10-23</t>
         </is>
       </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>مجاهد قسا امي</t>
+        </is>
+      </c>
       <c r="I329" t="inlineStr">
         <is>
           <t>كتيبة الصحابي حذيفة بن اليمان</t>
@@ -22730,6 +22781,11 @@
           <t>data/photos\718.jpg</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>data/frames\718_25.jpg;data/frames\718_28.jpg;data/frames\718_30.jpg;data/frames\718_32.jpg;data/frames\718_35.jpg</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>2026-05-02 13:01</t>
@@ -22742,7 +22798,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>partial_birth</t>
         </is>
       </c>
       <c r="P329" t="inlineStr">
@@ -22765,12 +22821,21 @@
           <t>صلاح الدين يوسف بربخ</t>
         </is>
       </c>
-      <c r="D330" s="1" t="inlineStr"/>
+      <c r="D330" s="1" t="inlineStr">
+        <is>
+          <t>1995-01-27</t>
+        </is>
+      </c>
       <c r="E330" s="1" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I330" t="inlineStr">
         <is>
           <t>كتيبة الصحابي أسامة بن زيد</t>
@@ -22786,6 +22851,11 @@
           <t>data/photos\720.jpg</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>data/frames\720_25.jpg;data/frames\720_28.jpg;data/frames\720_30.jpg;data/frames\720_32.jpg;data/frames\720_35.jpg</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>2026-05-02 14:59</t>
@@ -22798,7 +22868,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P330" t="inlineStr">
@@ -22821,12 +22891,21 @@
           <t>محمد سعيد حمدان</t>
         </is>
       </c>
-      <c r="D331" s="1" t="inlineStr"/>
+      <c r="D331" s="1" t="inlineStr">
+        <is>
+          <t>1987-08-11</t>
+        </is>
+      </c>
       <c r="E331" s="1" t="inlineStr">
         <is>
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I331" t="inlineStr">
         <is>
           <t>كتيبة الصحابي حذيفة بن اليمان</t>
@@ -22842,6 +22921,11 @@
           <t>data/photos\722.jpg</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>data/frames\722_25.jpg;data/frames\722_28.jpg;data/frames\722_30.jpg;data/frames\722_32.jpg;data/frames\722_35.jpg</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>2026-05-02 16:28</t>
@@ -22854,7 +22938,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P331" t="inlineStr">
@@ -22877,12 +22961,21 @@
           <t>خالد درويش ابو رزق</t>
         </is>
       </c>
-      <c r="D332" s="1" t="inlineStr"/>
+      <c r="D332" s="1" t="inlineStr">
+        <is>
+          <t>1996-10-10</t>
+        </is>
+      </c>
       <c r="E332" s="1" t="inlineStr">
         <is>
           <t>2023-10-07</t>
         </is>
       </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I332" t="inlineStr">
         <is>
           <t>كتيبة الصحابي مصعب بن عمير</t>
@@ -22898,6 +22991,11 @@
           <t>data/photos\724.jpg</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>data/frames\724_25.jpg;data/frames\724_28.jpg;data/frames\724_30.jpg;data/frames\724_32.jpg;data/frames\724_35.jpg</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>2026-05-02 18:01</t>
@@ -22910,7 +23008,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P332" t="inlineStr">
@@ -22933,12 +23031,21 @@
           <t>ماهر عبد الحكيم عرفات</t>
         </is>
       </c>
-      <c r="D333" s="1" t="inlineStr"/>
+      <c r="D333" s="1" t="inlineStr">
+        <is>
+          <t>1998-09-26</t>
+        </is>
+      </c>
       <c r="E333" s="1" t="inlineStr">
         <is>
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I333" t="inlineStr">
         <is>
           <t>كتيبة الصحابي أسد الله حمزة</t>
@@ -22954,6 +23061,11 @@
           <t>data/photos\726.jpg</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>data/frames\726_25.jpg;data/frames\726_28.jpg;data/frames\726_30.jpg;data/frames\726_32.jpg;data/frames\726_35.jpg</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>2026-05-02 19:30</t>
@@ -22966,7 +23078,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P333" t="inlineStr">
@@ -22989,12 +23101,21 @@
           <t>شادي طلال الحداد</t>
         </is>
       </c>
-      <c r="D334" s="1" t="inlineStr"/>
+      <c r="D334" s="1" t="inlineStr">
+        <is>
+          <t>1990-08-22</t>
+        </is>
+      </c>
       <c r="E334" s="1" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>الشهيد القائد الميداني شادي طلال الحداد كتيبة الصبرة وتل الإسلام لواء غزة</t>
+        </is>
+      </c>
       <c r="I334" t="inlineStr">
         <is>
           <t>كتيبة الصبرة وتل الإسلام</t>
@@ -23010,6 +23131,11 @@
           <t>data/photos\728.jpg</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>data/frames\728_25.jpg;data/frames\728_28.jpg;data/frames\728_30.jpg;data/frames\728_32.jpg;data/frames\728_35.jpg</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>2026-05-03 07:09</t>
@@ -23022,7 +23148,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P334" t="inlineStr">
@@ -23045,8 +23171,17 @@
           <t>موسي سمير شلدان</t>
         </is>
       </c>
-      <c r="D335" s="1" t="inlineStr"/>
+      <c r="D335" s="1" t="inlineStr">
+        <is>
+          <t>1987-05-23</t>
+        </is>
+      </c>
       <c r="E335" s="1" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>قائد سرية</t>
+        </is>
+      </c>
       <c r="I335" t="inlineStr">
         <is>
           <t>كتيبة الزيتون</t>
@@ -23057,6 +23192,11 @@
           <t>لواء غزة</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>data/frames\732_25.jpg;data/frames\732_28.jpg;data/frames\732_30.jpg;data/frames\732_32.jpg;data/frames\732_35.jpg</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>2026-05-03 10:52</t>
@@ -23069,7 +23209,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>photo_only_no_dates</t>
+          <t>partial_martyrdom</t>
         </is>
       </c>
       <c r="P335" t="inlineStr">
@@ -23092,12 +23232,21 @@
           <t>كريم نبيل ابو عرجه</t>
         </is>
       </c>
-      <c r="D336" s="1" t="inlineStr"/>
+      <c r="D336" s="1" t="inlineStr">
+        <is>
+          <t>1998-06-22</t>
+        </is>
+      </c>
       <c r="E336" s="1" t="inlineStr">
         <is>
           <t>2024-01-30</t>
         </is>
       </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I336" t="inlineStr">
         <is>
           <t>كتيبة الصبرة وتل الإسلام</t>
@@ -23113,6 +23262,11 @@
           <t>data/photos\734.jpg</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>data/frames\734_25.jpg;data/frames\734_28.jpg;data/frames\734_30.jpg;data/frames\734_32.jpg;data/frames\734_35.jpg</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>2026-05-03 13:03</t>
@@ -23125,7 +23279,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P336" t="inlineStr">
@@ -23148,12 +23302,21 @@
           <t>اسامه تيسير شريم</t>
         </is>
       </c>
-      <c r="D337" s="1" t="inlineStr"/>
+      <c r="D337" s="1" t="inlineStr">
+        <is>
+          <t>1995-01-24</t>
+        </is>
+      </c>
       <c r="E337" s="1" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="J337" t="inlineStr">
         <is>
           <t>لواء غزة</t>
@@ -23164,6 +23327,11 @@
           <t>data/photos\736.jpg</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>data/frames\736_25.jpg;data/frames\736_28.jpg;data/frames\736_30.jpg;data/frames\736_32.jpg;data/frames\736_35.jpg</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>2026-05-03 16:39</t>
@@ -23176,7 +23344,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P337" t="inlineStr">
@@ -23199,12 +23367,21 @@
           <t>عبد الحميد محمود ابو فايد</t>
         </is>
       </c>
-      <c r="D338" s="1" t="inlineStr"/>
+      <c r="D338" s="1" t="inlineStr">
+        <is>
+          <t>1986-08-05</t>
+        </is>
+      </c>
       <c r="E338" s="1" t="inlineStr">
         <is>
           <t>2023-12-27</t>
         </is>
       </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>قائدسرية</t>
+        </is>
+      </c>
       <c r="I338" t="inlineStr">
         <is>
           <t>كتيبة الرضوان</t>
@@ -23220,6 +23397,11 @@
           <t>data/photos\738.jpg</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>data/frames\738_25.jpg;data/frames\738_28.jpg;data/frames\738_30.jpg;data/frames\738_32.jpg;data/frames\738_35.jpg</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>2026-05-03 18:44</t>
@@ -23232,7 +23414,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
@@ -23255,12 +23437,21 @@
           <t>محمد حسين الايوبي</t>
         </is>
       </c>
-      <c r="D339" s="1" t="inlineStr"/>
+      <c r="D339" s="1" t="inlineStr">
+        <is>
+          <t>1994-05-25</t>
+        </is>
+      </c>
       <c r="E339" s="1" t="inlineStr">
         <is>
           <t>2024-08-26</t>
         </is>
       </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I339" t="inlineStr">
         <is>
           <t>كتيبة الصبرة وتل الإسلام</t>
@@ -23276,6 +23467,11 @@
           <t>data/photos\740.jpg</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>data/frames\740_25.jpg;data/frames\740_28.jpg;data/frames\740_30.jpg;data/frames\740_32.jpg;data/frames\740_35.jpg</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>2026-05-03 19:34</t>
@@ -23288,7 +23484,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P339" t="inlineStr">
@@ -23311,12 +23507,21 @@
           <t>رائد ابراهيم الصوالحي</t>
         </is>
       </c>
-      <c r="D340" s="1" t="inlineStr"/>
+      <c r="D340" s="1" t="inlineStr">
+        <is>
+          <t>1979-06-14</t>
+        </is>
+      </c>
       <c r="E340" s="1" t="inlineStr">
         <is>
           <t>/ 21 أكتوبر</t>
         </is>
       </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>قائ د فصيل نلج مده</t>
+        </is>
+      </c>
       <c r="I340" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد الشمالي</t>
@@ -23332,6 +23537,11 @@
           <t>data/photos\742.jpg</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>data/frames\742_25.jpg;data/frames\742_28.jpg;data/frames\742_30.jpg;data/frames\742_32.jpg;data/frames\742_35.jpg</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>2026-05-04 07:00</t>
@@ -23344,7 +23554,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P340" t="inlineStr">
@@ -23367,12 +23577,21 @@
           <t>ابراهيم عبد الرحيم منصور</t>
         </is>
       </c>
-      <c r="D341" s="1" t="inlineStr"/>
+      <c r="D341" s="1" t="inlineStr">
+        <is>
+          <t>1998-08-24</t>
+        </is>
+      </c>
       <c r="E341" s="1" t="inlineStr">
         <is>
           <t>2024-06-15</t>
         </is>
       </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>نائب قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I341" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو شمالة</t>
@@ -23388,6 +23607,11 @@
           <t>data/photos\744.jpg</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>data/frames\744_25.jpg;data/frames\744_28.jpg;data/frames\744_30.jpg;data/frames\744_32.jpg;data/frames\744_35.jpg</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>2026-05-04 09:01</t>
@@ -23400,7 +23624,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P341" t="inlineStr">
@@ -23423,12 +23647,21 @@
           <t>طارق علي المغربي</t>
         </is>
       </c>
-      <c r="D342" s="1" t="inlineStr"/>
+      <c r="D342" s="1" t="inlineStr">
+        <is>
+          <t>1985-08-06</t>
+        </is>
+      </c>
       <c r="E342" s="1" t="inlineStr">
         <is>
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>قائد سرية</t>
+        </is>
+      </c>
       <c r="I342" t="inlineStr">
         <is>
           <t>كتيبة الشهيد رائد العطار</t>
@@ -23444,6 +23677,11 @@
           <t>data/photos\746.jpg</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>data/frames\746_25.jpg;data/frames\746_28.jpg;data/frames\746_30.jpg;data/frames\746_32.jpg;data/frames\746_35.jpg</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>2026-05-04 11:00</t>
@@ -23456,7 +23694,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P342" t="inlineStr">
@@ -23479,12 +23717,21 @@
           <t>عنتر جهاد عاشور</t>
         </is>
       </c>
-      <c r="D343" s="1" t="inlineStr"/>
+      <c r="D343" s="1" t="inlineStr">
+        <is>
+          <t>1977-10-07</t>
+        </is>
+      </c>
       <c r="E343" s="1" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I343" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو حرب</t>
@@ -23500,6 +23747,11 @@
           <t>data/photos\748.jpg</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>data/frames\748_25.jpg;data/frames\748_28.jpg;data/frames\748_30.jpg;data/frames\748_32.jpg;data/frames\748_35.jpg</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>2026-05-04 12:58</t>
@@ -23512,7 +23764,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P343" t="inlineStr">
@@ -23541,6 +23793,11 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>قائد سرية</t>
+        </is>
+      </c>
       <c r="I344" t="inlineStr">
         <is>
           <t>كتيبة الشهيد رائد العطار</t>
@@ -23556,6 +23813,11 @@
           <t>data/photos\750.jpg</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>data/frames\750_25.jpg;data/frames\750_28.jpg;data/frames\750_30.jpg;data/frames\750_32.jpg;data/frames\750_35.jpg</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>2026-05-04 14:59</t>
@@ -23568,7 +23830,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>partial_birth</t>
         </is>
       </c>
       <c r="P344" t="inlineStr">
@@ -23591,12 +23853,21 @@
           <t>ابراهيم جميل البواب</t>
         </is>
       </c>
-      <c r="D345" s="1" t="inlineStr"/>
+      <c r="D345" s="1" t="inlineStr">
+        <is>
+          <t>1990-05-27</t>
+        </is>
+      </c>
       <c r="E345" s="1" t="inlineStr">
         <is>
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>نائب قائد سرية</t>
+        </is>
+      </c>
       <c r="I345" t="inlineStr">
         <is>
           <t>كتيبة الشهيد رائد العطار</t>
@@ -23612,6 +23883,11 @@
           <t>data/photos\752.jpg</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>data/frames\752_25.jpg;data/frames\752_28.jpg;data/frames\752_30.jpg;data/frames\752_32.jpg;data/frames\752_35.jpg</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>2026-05-04 16:29</t>
@@ -23624,7 +23900,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P345" t="inlineStr">
@@ -23647,7 +23923,11 @@
           <t>نمر راقي زبن "ابو عمر"</t>
         </is>
       </c>
-      <c r="D346" s="1" t="inlineStr"/>
+      <c r="D346" s="1" t="inlineStr">
+        <is>
+          <t>1975-01-23</t>
+        </is>
+      </c>
       <c r="E346" s="1" t="inlineStr">
         <is>
           <t>2024-07-13</t>
@@ -23658,6 +23938,11 @@
           <t>data/photos\754.jpg</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>data/frames\754_25.jpg;data/frames\754_28.jpg;data/frames\754_30.jpg;data/frames\754_32.jpg;data/frames\754_35.jpg</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>2026-05-04 18:42</t>
@@ -23670,7 +23955,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P346" t="inlineStr">
@@ -23693,12 +23978,21 @@
           <t>احمد عبد الخالق القططي</t>
         </is>
       </c>
-      <c r="D347" s="1" t="inlineStr"/>
+      <c r="D347" s="1" t="inlineStr">
+        <is>
+          <t>1994-03-16</t>
+        </is>
+      </c>
       <c r="E347" s="1" t="inlineStr">
         <is>
           <t>2024-06-15</t>
         </is>
       </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I347" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو شمالة</t>
@@ -23714,6 +24008,11 @@
           <t>data/photos\756.jpg</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>data/frames\756_25.jpg;data/frames\756_28.jpg;data/frames\756_30.jpg;data/frames\756_32.jpg;data/frames\756_35.jpg</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>2026-05-04 19:18</t>
@@ -23726,7 +24025,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P347" t="inlineStr">
@@ -23749,12 +24048,21 @@
           <t>همام سالم المصري</t>
         </is>
       </c>
-      <c r="D348" s="1" t="inlineStr"/>
+      <c r="D348" s="1" t="inlineStr">
+        <is>
+          <t>1987-02-28</t>
+        </is>
+      </c>
       <c r="E348" s="1" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>قائد سرية</t>
+        </is>
+      </c>
       <c r="I348" t="inlineStr">
         <is>
           <t>كتيبة الشهيد رائد العطار</t>
@@ -23770,6 +24078,11 @@
           <t>data/photos\758.jpg</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>data/frames\758_25.jpg;data/frames\758_28.jpg;data/frames\758_30.jpg;data/frames\758_32.jpg;data/frames\758_35.jpg</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>2026-05-04 20:01</t>
@@ -23782,7 +24095,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P348" t="inlineStr">
@@ -23805,12 +24118,21 @@
           <t>محمد اكرم شبات</t>
         </is>
       </c>
-      <c r="D349" s="1" t="inlineStr"/>
+      <c r="D349" s="1" t="inlineStr">
+        <is>
+          <t>1983-12-12</t>
+        </is>
+      </c>
       <c r="E349" s="1" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
       </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>قائسد سريحة</t>
+        </is>
+      </c>
       <c r="I349" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -23826,6 +24148,11 @@
           <t>data/photos\760.jpg</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>data/frames\760_25.jpg;data/frames\760_28.jpg;data/frames\760_30.jpg;data/frames\760_32.jpg;data/frames\760_35.jpg</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>2026-05-05 08:51</t>
@@ -23838,7 +24165,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P349" t="inlineStr">
@@ -23861,12 +24188,21 @@
           <t>صائب شوقي عدوان</t>
         </is>
       </c>
-      <c r="D350" s="1" t="inlineStr"/>
+      <c r="D350" s="1" t="inlineStr">
+        <is>
+          <t>1993-03-23</t>
+        </is>
+      </c>
       <c r="E350" s="1" t="inlineStr">
         <is>
           <t>2024-07-27</t>
         </is>
       </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>نائب قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I350" t="inlineStr">
         <is>
           <t>كتيبة الشهيد نضال ناصر</t>
@@ -23882,6 +24218,11 @@
           <t>data/photos\762.jpg</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>data/frames\762_25.jpg;data/frames\762_28.jpg;data/frames\762_30.jpg;data/frames\762_32.jpg;data/frames\762_35.jpg</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>2026-05-05 11:02</t>
@@ -23894,7 +24235,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P350" t="inlineStr">
@@ -23917,12 +24258,21 @@
           <t>اسماعيل اديب الحوراني</t>
         </is>
       </c>
-      <c r="D351" s="1" t="inlineStr"/>
+      <c r="D351" s="1" t="inlineStr">
+        <is>
+          <t>1998-07-20</t>
+        </is>
+      </c>
       <c r="E351" s="1" t="inlineStr">
         <is>
           <t>/23</t>
         </is>
       </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>قائسد فصيل</t>
+        </is>
+      </c>
       <c r="I351" t="inlineStr">
         <is>
           <t>كتيبة الشهيد عماد عقل</t>
@@ -23938,6 +24288,11 @@
           <t>data/photos\764.jpg</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>data/frames\764_25.jpg;data/frames\764_28.jpg;data/frames\764_30.jpg;data/frames\764_32.jpg;data/frames\764_35.jpg</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>2026-05-05 12:59</t>
@@ -23950,7 +24305,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -23973,12 +24328,21 @@
           <t>عصام محمود الحمدين</t>
         </is>
       </c>
-      <c r="D352" s="1" t="inlineStr"/>
+      <c r="D352" s="1" t="inlineStr">
+        <is>
+          <t>1984-12-22</t>
+        </is>
+      </c>
       <c r="E352" s="1" t="inlineStr">
         <is>
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I352" t="inlineStr">
         <is>
           <t>كتيبة الشهيد نضال ناصر</t>
@@ -23994,6 +24358,11 @@
           <t>data/photos\766.jpg</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>data/frames\766_25.jpg;data/frames\766_28.jpg;data/frames\766_30.jpg;data/frames\766_32.jpg;data/frames\766_35.jpg</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>2026-05-05 15:33</t>
@@ -24006,7 +24375,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P352" t="inlineStr">
@@ -24029,12 +24398,21 @@
           <t>حسين اسامه نصير</t>
         </is>
       </c>
-      <c r="D353" s="1" t="inlineStr"/>
+      <c r="D353" s="1" t="inlineStr">
+        <is>
+          <t>1993-03-07</t>
+        </is>
+      </c>
       <c r="E353" s="1" t="inlineStr">
         <is>
           <t>2025-01-13</t>
         </is>
       </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>قائسد فصيل</t>
+        </is>
+      </c>
       <c r="I353" t="inlineStr">
         <is>
           <t>كتيبة الشهيد نضال ناصر</t>
@@ -24050,6 +24428,11 @@
           <t>data/photos\768.jpg</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>data/frames\768_25.jpg;data/frames\768_28.jpg;data/frames\768_30.jpg;data/frames\768_32.jpg;data/frames\768_35.jpg</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>2026-05-05 17:05</t>
@@ -24062,7 +24445,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P353" t="inlineStr">
@@ -24085,12 +24468,21 @@
           <t>شادي محمد المبحوح</t>
         </is>
       </c>
-      <c r="D354" s="1" t="inlineStr"/>
+      <c r="D354" s="1" t="inlineStr">
+        <is>
+          <t>1981-11-27</t>
+        </is>
+      </c>
       <c r="E354" s="1" t="inlineStr">
         <is>
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>قائد سرية</t>
+        </is>
+      </c>
       <c r="I354" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -24106,6 +24498,11 @@
           <t>data/photos\770.jpg</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>data/frames\770_25.jpg;data/frames\770_28.jpg;data/frames\770_30.jpg;data/frames\770_32.jpg;data/frames\770_35.jpg</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>2026-05-05 19:41</t>
@@ -24118,7 +24515,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P354" t="inlineStr">
@@ -24141,12 +24538,21 @@
           <t>محمد جميل الاسطل</t>
         </is>
       </c>
-      <c r="D355" s="1" t="inlineStr"/>
+      <c r="D355" s="1" t="inlineStr">
+        <is>
+          <t>1992-06-11</t>
+        </is>
+      </c>
       <c r="E355" s="1" t="inlineStr">
         <is>
           <t>2024-01-10</t>
         </is>
       </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I355" t="inlineStr">
         <is>
           <t>كتيبة الصحابي مصعب بن عمير</t>
@@ -24162,6 +24568,11 @@
           <t>data/photos\772.jpg</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>data/frames\772_25.jpg;data/frames\772_28.jpg;data/frames\772_30.jpg;data/frames\772_32.jpg;data/frames\772_35.jpg</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>2026-05-06 07:18</t>
@@ -24174,7 +24585,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P355" t="inlineStr">
@@ -24197,12 +24608,21 @@
           <t>مصطفي كمال كلاب</t>
         </is>
       </c>
-      <c r="D356" s="1" t="inlineStr"/>
+      <c r="D356" s="1" t="inlineStr">
+        <is>
+          <t>1991-03-03</t>
+        </is>
+      </c>
       <c r="E356" s="1" t="inlineStr">
         <is>
           <t>2023-12-03</t>
         </is>
       </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I356" t="inlineStr">
         <is>
           <t>كتيبة الصحابي مصعب بن عمير</t>
@@ -24218,6 +24638,11 @@
           <t>data/photos\774.jpg</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>data/frames\774_25.jpg;data/frames\774_28.jpg;data/frames\774_30.jpg;data/frames\774_32.jpg;data/frames\774_35.jpg</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>2026-05-06 09:06</t>
@@ -24230,7 +24655,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P356" t="inlineStr">
@@ -24253,12 +24678,21 @@
           <t>محمد رسمي بركه</t>
         </is>
       </c>
-      <c r="D357" s="1" t="inlineStr"/>
+      <c r="D357" s="1" t="inlineStr">
+        <is>
+          <t>1989-05-13</t>
+        </is>
+      </c>
       <c r="E357" s="1" t="inlineStr">
         <is>
           <t>2025-07-05</t>
         </is>
       </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I357" t="inlineStr">
         <is>
           <t>كتيبة الصحابي أسد الله حمزة</t>
@@ -24274,6 +24708,11 @@
           <t>data/photos\776.jpg</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>data/frames\776_25.jpg;data/frames\776_28.jpg;data/frames\776_30.jpg;data/frames\776_32.jpg;data/frames\776_35.jpg</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>2026-05-06 11:08</t>
@@ -24286,7 +24725,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P357" t="inlineStr">
@@ -24309,12 +24748,21 @@
           <t>ناجي فوزي ابو رجيله</t>
         </is>
       </c>
-      <c r="D358" s="1" t="inlineStr"/>
+      <c r="D358" s="1" t="inlineStr">
+        <is>
+          <t>1979-05-25</t>
+        </is>
+      </c>
       <c r="E358" s="1" t="inlineStr">
         <is>
           <t>2023-10-11</t>
         </is>
       </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I358" t="inlineStr">
         <is>
           <t>كتيبة الصحابي أسد الله حمزة</t>
@@ -24330,6 +24778,11 @@
           <t>data/photos\778.jpg</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>data/frames\778_25.jpg;data/frames\778_28.jpg;data/frames\778_30.jpg;data/frames\778_32.jpg;data/frames\778_35.jpg</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>2026-05-06 13:38</t>
@@ -24342,7 +24795,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P358" t="inlineStr">
@@ -24365,12 +24818,21 @@
           <t>مازن سالم القرا</t>
         </is>
       </c>
-      <c r="D359" s="1" t="inlineStr"/>
+      <c r="D359" s="1" t="inlineStr">
+        <is>
+          <t>1996-06-09</t>
+        </is>
+      </c>
       <c r="E359" s="1" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I359" t="inlineStr">
         <is>
           <t>كتيبة الصحابي أسد الله حمزة</t>
@@ -24386,6 +24848,11 @@
           <t>data/photos\780.jpg</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>data/frames\780_25.jpg;data/frames\780_28.jpg;data/frames\780_30.jpg;data/frames\780_32.jpg;data/frames\780_35.jpg</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>2026-05-06 16:01</t>
@@ -24398,7 +24865,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P359" t="inlineStr">
@@ -24421,12 +24888,21 @@
           <t>محمد عماد العبادله</t>
         </is>
       </c>
-      <c r="D360" s="1" t="inlineStr"/>
+      <c r="D360" s="1" t="inlineStr">
+        <is>
+          <t>1994-11-02</t>
+        </is>
+      </c>
       <c r="E360" s="1" t="inlineStr">
         <is>
           <t>2024-03-24</t>
         </is>
       </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I360" t="inlineStr">
         <is>
           <t>كتيبة الصحابي مصعب بن عمير</t>
@@ -24442,6 +24918,11 @@
           <t>data/photos\782.jpg</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>data/frames\782_25.jpg;data/frames\782_28.jpg;data/frames\782_30.jpg;data/frames\782_32.jpg;data/frames\782_35.jpg</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>2026-05-06 17:25</t>
@@ -24454,7 +24935,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P360" t="inlineStr">
@@ -24477,12 +24958,21 @@
           <t>وسام ابراهيم شراب</t>
         </is>
       </c>
-      <c r="D361" s="1" t="inlineStr"/>
+      <c r="D361" s="1" t="inlineStr">
+        <is>
+          <t>1989-12-12</t>
+        </is>
+      </c>
       <c r="E361" s="1" t="inlineStr">
         <is>
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I361" t="inlineStr">
         <is>
           <t>كتيبة أسامة بن زيد</t>
@@ -24498,6 +24988,11 @@
           <t>data/photos\784.jpg</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>data/frames\784_25.jpg;data/frames\784_28.jpg;data/frames\784_30.jpg;data/frames\784_32.jpg;data/frames\784_35.jpg</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>2026-05-06 18:33</t>
@@ -24510,7 +25005,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P361" t="inlineStr">
@@ -24533,12 +25028,21 @@
           <t>تميم محمد ابو معروف</t>
         </is>
       </c>
-      <c r="D362" s="1" t="inlineStr"/>
+      <c r="D362" s="1" t="inlineStr">
+        <is>
+          <t>1998-12-30</t>
+        </is>
+      </c>
       <c r="E362" s="1" t="inlineStr">
         <is>
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I362" t="inlineStr">
         <is>
           <t>كتيبة أسامة بن زيد</t>
@@ -24554,6 +25058,11 @@
           <t>data/photos\786.jpg</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>data/frames\786_25.jpg;data/frames\786_28.jpg;data/frames\786_30.jpg;data/frames\786_32.jpg;data/frames\786_35.jpg</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>2026-05-06 19:38</t>
@@ -24566,7 +25075,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P362" t="inlineStr">
@@ -24589,12 +25098,21 @@
           <t>محمد جواد الواديه</t>
         </is>
       </c>
-      <c r="D363" s="1" t="inlineStr"/>
+      <c r="D363" s="1" t="inlineStr">
+        <is>
+          <t>1990-08-15</t>
+        </is>
+      </c>
       <c r="E363" s="1" t="inlineStr">
         <is>
           <t>2023-10-10</t>
         </is>
       </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>قائدسرية</t>
+        </is>
+      </c>
       <c r="J363" t="inlineStr">
         <is>
           <t>لواء غزة</t>
@@ -24605,6 +25123,11 @@
           <t>data/photos\788.jpg</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>data/frames\788_25.jpg;data/frames\788_28.jpg;data/frames\788_30.jpg;data/frames\788_32.jpg;data/frames\788_35.jpg</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>2026-05-07 07:05</t>
@@ -24617,7 +25140,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P363" t="inlineStr">
@@ -24640,12 +25163,21 @@
           <t>غالب فرج الدحدوح</t>
         </is>
       </c>
-      <c r="D364" s="1" t="inlineStr"/>
+      <c r="D364" s="1" t="inlineStr">
+        <is>
+          <t>1994-11-27</t>
+        </is>
+      </c>
       <c r="E364" s="1" t="inlineStr">
         <is>
           <t>2024-02-20</t>
         </is>
       </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>قائسد فصيل</t>
+        </is>
+      </c>
       <c r="I364" t="inlineStr">
         <is>
           <t>كتيبة الزيتون</t>
@@ -24661,6 +25193,11 @@
           <t>data/photos\790.jpg</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>data/frames\790_25.jpg;data/frames\790_28.jpg;data/frames\790_30.jpg;data/frames\790_32.jpg;data/frames\790_35.jpg</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>2026-05-07 09:09</t>
@@ -24673,7 +25210,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P364" t="inlineStr">
@@ -24696,8 +25233,21 @@
           <t>ابراهيم عمر الغول</t>
         </is>
       </c>
-      <c r="D365" s="1" t="inlineStr"/>
-      <c r="E365" s="1" t="inlineStr"/>
+      <c r="D365" s="1" t="inlineStr">
+        <is>
+          <t>1988-03-31</t>
+        </is>
+      </c>
+      <c r="E365" s="1" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I365" t="inlineStr">
         <is>
           <t>كتيبة القدس</t>
@@ -24713,6 +25263,11 @@
           <t>data/photos\792.jpg</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>data/frames\792_25.jpg;data/frames\792_28.jpg;data/frames\792_30.jpg;data/frames\792_32.jpg;data/frames\792_35.jpg</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>2026-05-07 11:09</t>
@@ -24725,7 +25280,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>photo_only_no_dates</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P365" t="inlineStr">
@@ -24748,8 +25303,21 @@
           <t>عز الدين عاطف حسان</t>
         </is>
       </c>
-      <c r="D366" s="1" t="inlineStr"/>
-      <c r="E366" s="1" t="inlineStr"/>
+      <c r="D366" s="1" t="inlineStr">
+        <is>
+          <t>1993-03-13</t>
+        </is>
+      </c>
+      <c r="E366" s="1" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I366" t="inlineStr">
         <is>
           <t>كتيبة القدس</t>
@@ -24765,6 +25333,11 @@
           <t>data/photos\794.jpg</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>data/frames\794_25.jpg;data/frames\794_28.jpg;data/frames\794_30.jpg;data/frames\794_32.jpg;data/frames\794_35.jpg</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>2026-05-07 13:01</t>
@@ -24777,7 +25350,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>photo_only_no_dates</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P366" t="inlineStr">
@@ -24800,8 +25373,17 @@
           <t>عامر احمد ابو خليل</t>
         </is>
       </c>
-      <c r="D367" s="1" t="inlineStr"/>
+      <c r="D367" s="1" t="inlineStr">
+        <is>
+          <t>1984-10-10</t>
+        </is>
+      </c>
       <c r="E367" s="1" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I367" t="inlineStr">
         <is>
           <t>كتيبة القدس</t>
@@ -24817,6 +25399,11 @@
           <t>data/photos\796.jpg</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>data/frames\796_25.jpg;data/frames\796_28.jpg;data/frames\796_30.jpg;data/frames\796_32.jpg;data/frames\796_35.jpg</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>2026-05-07 15:04</t>
@@ -24829,7 +25416,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>photo_only_no_dates</t>
+          <t>partial_martyrdom</t>
         </is>
       </c>
       <c r="P367" t="inlineStr">
@@ -24852,7 +25439,11 @@
           <t>مؤيد سليمان قواسمه</t>
         </is>
       </c>
-      <c r="D368" s="1" t="inlineStr"/>
+      <c r="D368" s="1" t="inlineStr">
+        <is>
+          <t>1986-04-20</t>
+        </is>
+      </c>
       <c r="E368" s="1" t="inlineStr">
         <is>
           <t>2025-05-22</t>
@@ -24863,6 +25454,11 @@
           <t>data/photos\798.jpg</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>data/frames\798_25.jpg;data/frames\798_28.jpg;data/frames\798_30.jpg;data/frames\798_32.jpg;data/frames\798_35.jpg</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>2026-05-07 16:30</t>
@@ -24875,7 +25471,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P368" t="inlineStr">
@@ -24898,12 +25494,21 @@
           <t>موسي محمد الحيله</t>
         </is>
       </c>
-      <c r="D369" s="1" t="inlineStr"/>
+      <c r="D369" s="1" t="inlineStr">
+        <is>
+          <t>1986-11-15</t>
+        </is>
+      </c>
       <c r="E369" s="1" t="inlineStr">
         <is>
           <t>2025-07-20</t>
         </is>
       </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>نائب قائد فصيل</t>
+        </is>
+      </c>
       <c r="I369" t="inlineStr">
         <is>
           <t>كتيبة الصحابي حذيفة بن اليمان</t>
@@ -24919,6 +25524,11 @@
           <t>data/photos\800.jpg</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>data/frames\800_25.jpg;data/frames\800_28.jpg;data/frames\800_30.jpg;data/frames\800_32.jpg;data/frames\800_35.jpg</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>2026-05-07 18:20</t>
@@ -24931,7 +25541,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P369" t="inlineStr">
@@ -24954,12 +25564,21 @@
           <t>احمد خالد ابو عوده</t>
         </is>
       </c>
-      <c r="D370" s="1" t="inlineStr"/>
+      <c r="D370" s="1" t="inlineStr">
+        <is>
+          <t>1986-12-10</t>
+        </is>
+      </c>
       <c r="E370" s="1" t="inlineStr">
         <is>
           <t>2023-12-19</t>
         </is>
       </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I370" t="inlineStr">
         <is>
           <t>كتيبة الصحابي مصعب بن عمير</t>
@@ -24975,6 +25594,11 @@
           <t>data/photos\802.jpg</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>data/frames\802_25.jpg;data/frames\802_28.jpg;data/frames\802_30.jpg;data/frames\802_32.jpg;data/frames\802_35.jpg</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>2026-05-07 19:20</t>
@@ -24987,7 +25611,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P370" t="inlineStr">
@@ -25010,12 +25634,21 @@
           <t>هشام صلاح الدين سهمود</t>
         </is>
       </c>
-      <c r="D371" s="1" t="inlineStr"/>
+      <c r="D371" s="1" t="inlineStr">
+        <is>
+          <t>1989-09-14</t>
+        </is>
+      </c>
       <c r="E371" s="1" t="inlineStr">
         <is>
           <t>2025-05-14</t>
         </is>
       </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>مجاهد قسا مو</t>
+        </is>
+      </c>
       <c r="I371" t="inlineStr">
         <is>
           <t>كتيبة الصحابي أسد الله حمزة</t>
@@ -25031,6 +25664,11 @@
           <t>data/photos\804.jpg</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>data/frames\804_25.jpg;data/frames\804_28.jpg;data/frames\804_30.jpg;data/frames\804_32.jpg;data/frames\804_35.jpg</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>2026-05-07 20:21</t>
@@ -25043,7 +25681,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
@@ -25066,12 +25704,21 @@
           <t>يحيي منهل ابو عرمانه</t>
         </is>
       </c>
-      <c r="D372" s="1" t="inlineStr"/>
+      <c r="D372" s="1" t="inlineStr">
+        <is>
+          <t>2000-03-29</t>
+        </is>
+      </c>
       <c r="E372" s="1" t="inlineStr">
         <is>
           <t>2023-10-15</t>
         </is>
       </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>مجاهد قسامي</t>
+        </is>
+      </c>
       <c r="I372" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو شمالة</t>
@@ -25087,6 +25734,11 @@
           <t>data/photos\806.jpg</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>data/frames\806_25.jpg;data/frames\806_28.jpg;data/frames\806_30.jpg;data/frames\806_32.jpg;data/frames\806_35.jpg</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>2026-05-09 06:48</t>
@@ -25099,7 +25751,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
@@ -25122,12 +25774,21 @@
           <t>محمد اسماعيل الصوالحه</t>
         </is>
       </c>
-      <c r="D373" s="1" t="inlineStr"/>
+      <c r="D373" s="1" t="inlineStr">
+        <is>
+          <t>1980-12-02</t>
+        </is>
+      </c>
       <c r="E373" s="1" t="inlineStr">
         <is>
           <t>2024-05-17</t>
         </is>
       </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>نائب  قائد سرية</t>
+        </is>
+      </c>
       <c r="I373" t="inlineStr">
         <is>
           <t>كتيبة الشهيد رائد العطار</t>
@@ -25143,6 +25804,11 @@
           <t>data/photos\808.jpg</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>data/frames\808_25.jpg;data/frames\808_28.jpg;data/frames\808_30.jpg;data/frames\808_32.jpg;data/frames\808_35.jpg</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>2026-05-09 08:50</t>
@@ -25155,7 +25821,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P373" t="inlineStr">
@@ -25178,12 +25844,21 @@
           <t>رائد محمد شيخ العيد</t>
         </is>
       </c>
-      <c r="D374" s="1" t="inlineStr"/>
+      <c r="D374" s="1" t="inlineStr">
+        <is>
+          <t>1988-09-23</t>
+        </is>
+      </c>
       <c r="E374" s="1" t="inlineStr">
         <is>
           <t>2024-05-15</t>
         </is>
       </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>نائب قائدسريًة</t>
+        </is>
+      </c>
       <c r="I374" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو شمالة</t>
@@ -25199,6 +25874,11 @@
           <t>data/photos\810.jpg</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>data/frames\810_25.jpg;data/frames\810_28.jpg;data/frames\810_30.jpg;data/frames\810_32.jpg;data/frames\810_35.jpg</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>2026-05-09 11:08</t>
@@ -25211,7 +25891,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P374" t="inlineStr">
@@ -25234,12 +25914,21 @@
           <t>حسن عبد الحميد ابو معمر</t>
         </is>
       </c>
-      <c r="D375" s="1" t="inlineStr"/>
+      <c r="D375" s="1" t="inlineStr">
+        <is>
+          <t>1998-04-10</t>
+        </is>
+      </c>
       <c r="E375" s="1" t="inlineStr">
         <is>
           <t>2025-07-04</t>
         </is>
       </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>مجاهد قسا م</t>
+        </is>
+      </c>
       <c r="I375" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو حرب</t>
@@ -25255,6 +25944,11 @@
           <t>data/photos\812.jpg</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>data/frames\812_25.jpg;data/frames\812_28.jpg;data/frames\812_30.jpg;data/frames\812_32.jpg;data/frames\812_35.jpg</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>2026-05-09 12:56</t>
@@ -25267,7 +25961,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P375" t="inlineStr">
@@ -25290,12 +25984,21 @@
           <t>احمد محمد مقداد</t>
         </is>
       </c>
-      <c r="D376" s="1" t="inlineStr"/>
+      <c r="D376" s="1" t="inlineStr">
+        <is>
+          <t>2001-03-03</t>
+        </is>
+      </c>
       <c r="E376" s="1" t="inlineStr">
         <is>
           <t>2023-12-20</t>
         </is>
       </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>مجاهد قسامي</t>
+        </is>
+      </c>
       <c r="I376" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو حرب</t>
@@ -25311,6 +26014,11 @@
           <t>data/photos\814.jpg</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>data/frames\814_25.jpg;data/frames\814_28.jpg;data/frames\814_30.jpg;data/frames\814_32.jpg;data/frames\814_35.jpg</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>2026-05-09 14:30</t>
@@ -25323,7 +26031,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P376" t="inlineStr">
@@ -25346,12 +26054,21 @@
           <t>عرفه ياسر خفاجه</t>
         </is>
       </c>
-      <c r="D377" s="1" t="inlineStr"/>
+      <c r="D377" s="1" t="inlineStr">
+        <is>
+          <t>1991-06-21</t>
+        </is>
+      </c>
       <c r="E377" s="1" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I377" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو شمالة</t>
@@ -25367,6 +26084,11 @@
           <t>data/photos\816.jpg</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>data/frames\816_25.jpg;data/frames\816_28.jpg;data/frames\816_30.jpg;data/frames\816_32.jpg;data/frames\816_35.jpg</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>2026-05-09 16:33</t>
@@ -25379,7 +26101,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P377" t="inlineStr">
@@ -25402,12 +26124,21 @@
           <t>بلال عماد عبد العال</t>
         </is>
       </c>
-      <c r="D378" s="1" t="inlineStr"/>
+      <c r="D378" s="1" t="inlineStr">
+        <is>
+          <t>1997-07-17</t>
+        </is>
+      </c>
       <c r="E378" s="1" t="inlineStr">
         <is>
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>نائب قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I378" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو حرب</t>
@@ -25423,6 +26154,11 @@
           <t>data/photos\818.jpg</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>data/frames\818_25.jpg;data/frames\818_28.jpg;data/frames\818_30.jpg;data/frames\818_32.jpg;data/frames\818_35.jpg</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>2026-05-09 18:20</t>
@@ -25435,7 +26171,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P378" t="inlineStr">
@@ -25458,12 +26194,21 @@
           <t>تامر هاني عاشور</t>
         </is>
       </c>
-      <c r="D379" s="1" t="inlineStr"/>
+      <c r="D379" s="1" t="inlineStr">
+        <is>
+          <t>1997-11-06</t>
+        </is>
+      </c>
       <c r="E379" s="1" t="inlineStr">
         <is>
           <t>2024-04-27</t>
         </is>
       </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>نائب قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I379" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو حرب</t>
@@ -25479,6 +26224,11 @@
           <t>data/photos\820.jpg</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>data/frames\820_25.jpg;data/frames\820_28.jpg;data/frames\820_30.jpg;data/frames\820_32.jpg;data/frames\820_35.jpg</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>2026-05-09 19:28</t>
@@ -25491,7 +26241,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P379" t="inlineStr">
@@ -25514,12 +26264,21 @@
           <t>محمد محمد ابو سعاده</t>
         </is>
       </c>
-      <c r="D380" s="1" t="inlineStr"/>
+      <c r="D380" s="1" t="inlineStr">
+        <is>
+          <t>1996-10-23</t>
+        </is>
+      </c>
       <c r="E380" s="1" t="inlineStr">
         <is>
           <t>2023-10-09</t>
         </is>
       </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I380" t="inlineStr">
         <is>
           <t>كتيبة الشهيد فوزي أبو القرع</t>
@@ -25535,6 +26294,11 @@
           <t>data/photos\822.jpg</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>data/frames\822_25.jpg;data/frames\822_28.jpg;data/frames\822_30.jpg;data/frames\822_32.jpg;data/frames\822_35.jpg</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>2026-05-10 07:14</t>
@@ -25547,7 +26311,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P380" t="inlineStr">
@@ -25570,12 +26334,21 @@
           <t>ادهم رمزي جبر</t>
         </is>
       </c>
-      <c r="D381" s="1" t="inlineStr"/>
+      <c r="D381" s="1" t="inlineStr">
+        <is>
+          <t>1987-10-12</t>
+        </is>
+      </c>
       <c r="E381" s="1" t="inlineStr">
         <is>
           <t>2024-11-23</t>
         </is>
       </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>نائب قائد سرية</t>
+        </is>
+      </c>
       <c r="I381" t="inlineStr">
         <is>
           <t>كتيبة الشهيد سهيل زيادة</t>
@@ -25591,6 +26364,11 @@
           <t>data/photos\824.jpg</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>data/frames\824_25.jpg;data/frames\824_28.jpg;data/frames\824_30.jpg;data/frames\824_32.jpg;data/frames\824_35.jpg</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>2026-05-10 08:57</t>
@@ -25603,7 +26381,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P381" t="inlineStr">
@@ -25626,12 +26404,21 @@
           <t>يعقوب عنان البرش</t>
         </is>
       </c>
-      <c r="D382" s="1" t="inlineStr"/>
+      <c r="D382" s="1" t="inlineStr">
+        <is>
+          <t>1993-01-07</t>
+        </is>
+      </c>
       <c r="E382" s="1" t="inlineStr">
         <is>
           <t>2023-11-12</t>
         </is>
       </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I382" t="inlineStr">
         <is>
           <t>كتيبة الشهيد عبد الرؤوف نبهان</t>
@@ -25647,6 +26434,11 @@
           <t>data/photos\826.jpg</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>data/frames\826_25.jpg;data/frames\826_28.jpg;data/frames\826_30.jpg;data/frames\826_32.jpg;data/frames\826_35.jpg</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>2026-05-10 11:14</t>
@@ -25659,7 +26451,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P382" t="inlineStr">
@@ -25682,12 +26474,21 @@
           <t>نضال زهير سليمان</t>
         </is>
       </c>
-      <c r="D383" s="1" t="inlineStr"/>
+      <c r="D383" s="1" t="inlineStr">
+        <is>
+          <t>1987-10-05</t>
+        </is>
+      </c>
       <c r="E383" s="1" t="inlineStr">
         <is>
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I383" t="inlineStr">
         <is>
           <t>كتيبة الشهيد عبد الرؤوف نبهان</t>
@@ -25703,6 +26504,11 @@
           <t>data/photos\828.jpg</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>data/frames\828_25.jpg;data/frames\828_28.jpg;data/frames\828_30.jpg;data/frames\828_32.jpg;data/frames\828_35.jpg</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>2026-05-10 12:51</t>
@@ -25715,7 +26521,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P383" t="inlineStr">
@@ -25738,12 +26544,21 @@
           <t>محمود حسن الدباغ</t>
         </is>
       </c>
-      <c r="D384" s="1" t="inlineStr"/>
+      <c r="D384" s="1" t="inlineStr">
+        <is>
+          <t>1991-02-26</t>
+        </is>
+      </c>
       <c r="E384" s="1" t="inlineStr">
         <is>
           <t>2023-11-04</t>
         </is>
       </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>قائد سريًة</t>
+        </is>
+      </c>
       <c r="I384" t="inlineStr">
         <is>
           <t>كتيبة الشهيد فوزي أبو القرع</t>
@@ -25759,6 +26574,11 @@
           <t>data/photos\830.jpg</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>data/frames\830_25.jpg;data/frames\830_28.jpg;data/frames\830_30.jpg;data/frames\830_32.jpg;data/frames\830_35.jpg</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>2026-05-10 15:26</t>
@@ -25771,7 +26591,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P384" t="inlineStr">
@@ -25794,12 +26614,21 @@
           <t>كرم اكرم سمور</t>
         </is>
       </c>
-      <c r="D385" s="1" t="inlineStr"/>
+      <c r="D385" s="1" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
       <c r="E385" s="1" t="inlineStr">
         <is>
           <t>/ 02</t>
         </is>
       </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I385" t="inlineStr">
         <is>
           <t>كتيبة الشهيد عماد عقل</t>
@@ -25815,6 +26644,11 @@
           <t>data/photos\832.jpg</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>data/frames\832_25.jpg;data/frames\832_28.jpg;data/frames\832_30.jpg;data/frames\832_32.jpg;data/frames\832_35.jpg</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>2026-05-10 16:47</t>
@@ -25827,7 +26661,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P385" t="inlineStr">
@@ -25850,12 +26684,21 @@
           <t>بلال ماهر الحاطوم</t>
         </is>
       </c>
-      <c r="D386" s="1" t="inlineStr"/>
+      <c r="D386" s="1" t="inlineStr">
+        <is>
+          <t>1989-03-31</t>
+        </is>
+      </c>
       <c r="E386" s="1" t="inlineStr">
         <is>
           <t>2025-05-23</t>
         </is>
       </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I386" t="inlineStr">
         <is>
           <t>كتيبة الشهيد عماد عقل</t>
@@ -25871,6 +26714,11 @@
           <t>data/photos\834.jpg</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>data/frames\834_25.jpg;data/frames\834_28.jpg;data/frames\834_30.jpg;data/frames\834_32.jpg;data/frames\834_35.jpg</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>2026-05-10 17:39</t>
@@ -25883,7 +26731,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P386" t="inlineStr">
@@ -25906,12 +26754,21 @@
           <t>احمد جمال ابراهيم جراد</t>
         </is>
       </c>
-      <c r="D387" s="1" t="inlineStr"/>
+      <c r="D387" s="1" t="inlineStr">
+        <is>
+          <t>1989-08-05</t>
+        </is>
+      </c>
       <c r="E387" s="1" t="inlineStr">
         <is>
           <t>2023-10-28</t>
         </is>
       </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
       <c r="I387" t="inlineStr">
         <is>
           <t>كتيبة الشهيد فوزي أبو القرع</t>
@@ -25927,6 +26784,11 @@
           <t>data/photos\836.jpg</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>data/frames\836_25.jpg;data/frames\836_28.jpg;data/frames\836_30.jpg;data/frames\836_32.jpg;data/frames\836_35.jpg</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>2026-05-10 19:20</t>
@@ -25939,7 +26801,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
@@ -25962,12 +26824,21 @@
           <t>احمد ايمن حجازي</t>
         </is>
       </c>
-      <c r="D388" s="1" t="inlineStr"/>
+      <c r="D388" s="1" t="inlineStr">
+        <is>
+          <t>1995-11-22</t>
+        </is>
+      </c>
       <c r="E388" s="1" t="inlineStr">
         <is>
           <t>2025-07-21</t>
         </is>
       </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>مجاهد قسا مو</t>
+        </is>
+      </c>
       <c r="I388" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -25983,6 +26854,11 @@
           <t>data/photos\838.jpg</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>data/frames\838_25.jpg;data/frames\838_28.jpg;data/frames\838_30.jpg;data/frames\838_32.jpg;data/frames\838_35.jpg</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>2026-05-11 07:02</t>
@@ -25995,7 +26871,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P388" t="inlineStr">
@@ -26018,12 +26894,21 @@
           <t>احمد ماجد صلاح</t>
         </is>
       </c>
-      <c r="D389" s="1" t="inlineStr"/>
+      <c r="D389" s="1" t="inlineStr">
+        <is>
+          <t>1992-10-05</t>
+        </is>
+      </c>
       <c r="E389" s="1" t="inlineStr">
         <is>
           <t>2025-07-14</t>
         </is>
       </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>نائب قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I389" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -26039,6 +26924,11 @@
           <t>data/photos\840.jpg</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>data/frames\840_25.jpg;data/frames\840_28.jpg;data/frames\840_30.jpg;data/frames\840_32.jpg;data/frames\840_35.jpg</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>2026-05-11 09:08</t>
@@ -26051,7 +26941,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P389" t="inlineStr">
@@ -26074,12 +26964,21 @@
           <t>بلال جميل طبش</t>
         </is>
       </c>
-      <c r="D390" s="1" t="inlineStr"/>
+      <c r="D390" s="1" t="inlineStr">
+        <is>
+          <t>1995-07-20</t>
+        </is>
+      </c>
       <c r="E390" s="1" t="inlineStr">
         <is>
           <t>2023-11-04</t>
         </is>
       </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
       <c r="I390" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -26095,6 +26994,11 @@
           <t>data/photos\842.jpg</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>data/frames\842_25.jpg;data/frames\842_28.jpg;data/frames\842_30.jpg;data/frames\842_32.jpg;data/frames\842_35.jpg</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>2026-05-11 11:38</t>
@@ -26107,10 +27011,2582 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>photo_only_no_birth</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P390" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>844</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>محمود نايف أبو شمالة</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>محمود نايف ابو شماله</t>
+        </is>
+      </c>
+      <c r="D391" s="1" t="inlineStr">
+        <is>
+          <t>1990-10-31</t>
+        </is>
+      </c>
+      <c r="E391" s="1" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>نائب قائد مجموعة</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>كتيبة المدفعية</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>لواء خانيونس</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>data/photos\844.jpg</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>data/frames\844_28.jpg;data/frames\844_30.jpg;data/frames\844_32.jpg</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:15</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/844</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>846</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>وحيد سليمان أبو عرام</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>وحيد سليمان ابو عرام</t>
+        </is>
+      </c>
+      <c r="D392" s="1" t="inlineStr">
+        <is>
+          <t>1990-10-31</t>
+        </is>
+      </c>
+      <c r="E392" s="1" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>مجاهد قسا مو</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>كتيبة المدفعية</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>لواء خانيونس</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>data/photos\846.jpg</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>data/frames\846_28.jpg;data/frames\846_30.jpg;data/frames\846_32.jpg</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:00</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/846</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>848</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>يوسف محمد أبو شمالة</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>يوسف محمد ابو شماله</t>
+        </is>
+      </c>
+      <c r="D393" s="1" t="inlineStr">
+        <is>
+          <t>1990-05-10</t>
+        </is>
+      </c>
+      <c r="E393" s="1" t="inlineStr">
+        <is>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>مجاهد قسا مو</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>كتيبة المدفعية</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>لواء خانيونس</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>data/photos\848.jpg</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>data/frames\848_28.jpg;data/frames\848_30.jpg;data/frames\848_32.jpg</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2026-05-11 16:36</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/848</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>850</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>حسام مهدي النجار</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>حسام مهدي النجار</t>
+        </is>
+      </c>
+      <c r="D394" s="1" t="inlineStr"/>
+      <c r="E394" s="1" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>كتيبة المدفعية</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>لواء خانيونس</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>data/photos\850.jpg</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>data/frames\850_28.jpg;data/frames\850_30.jpg;data/frames\850_32.jpg</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:13</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/850</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>partial_birth</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>852</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>أحمد عبد الحكيم أبو ظاهر</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>احمد عبد الحكيم ابو ظاهر</t>
+        </is>
+      </c>
+      <c r="D395" s="1" t="inlineStr">
+        <is>
+          <t>1988-02-07</t>
+        </is>
+      </c>
+      <c r="E395" s="1" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>مجاهد قسا مو</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>كتيبة المدفعية</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>لواء خانيونس</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>data/photos\852.jpg</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>data/frames\852_28.jpg;data/frames\852_30.jpg;data/frames\852_32.jpg</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:18</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/852</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>854</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>رامي عدنان السكني</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>رامي عدنان السكني</t>
+        </is>
+      </c>
+      <c r="D396" s="1" t="inlineStr">
+        <is>
+          <t>1982-10-10</t>
+        </is>
+      </c>
+      <c r="E396" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>قائدسرية</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>كتيبة التفاح والدرج</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>لواء غزة</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>data/photos\854.jpg</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>data/frames\854_28.jpg;data/frames\854_30.jpg;data/frames\854_32.jpg</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2026-05-12 07:03</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/854</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>856</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>محمد خميس النونو</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>محمد خميس النونو</t>
+        </is>
+      </c>
+      <c r="D397" s="1" t="inlineStr">
+        <is>
+          <t>1993-12-30</t>
+        </is>
+      </c>
+      <c r="E397" s="1" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>كتيبة الرضوان</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>لواء غزة</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>data/photos\856.jpg</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>data/frames\856_28.jpg;data/frames\856_30.jpg;data/frames\856_32.jpg</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-05-12 09:02</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/856</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>858</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>ياسر هاني أبو هين</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>ياسر هاني ابو هين</t>
+        </is>
+      </c>
+      <c r="D398" s="1" t="inlineStr">
+        <is>
+          <t>1992-12-14</t>
+        </is>
+      </c>
+      <c r="E398" s="1" t="inlineStr">
+        <is>
+          <t>2023-12-07</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>قائدفصيل</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>كتيبة الشجاعية</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>لواء غزة</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>data/photos\858.jpg</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>data/frames\858_28.jpg;data/frames\858_30.jpg;data/frames\858_32.jpg</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:03</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/858</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>860</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>عز الدين هاني أبو جياب</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>عز الدين هاني ابو جياب</t>
+        </is>
+      </c>
+      <c r="D399" s="1" t="inlineStr">
+        <is>
+          <t>1993-03-16</t>
+        </is>
+      </c>
+      <c r="E399" s="1" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>كتيبة الرضوان</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>لواء غزة</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>data/photos\860.jpg</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>data/frames\860_28.jpg;data/frames\860_30.jpg;data/frames\860_32.jpg</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:42</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/860</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>862</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>عماد عبد الله قريقع</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>عماد عبد الله قريقع</t>
+        </is>
+      </c>
+      <c r="D400" s="1" t="inlineStr">
+        <is>
+          <t>1987-12-05</t>
+        </is>
+      </c>
+      <c r="E400" s="1" t="inlineStr">
+        <is>
+          <t>2023-12-07</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>نائب قائد كتيبة</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>كتيبة الشجاعية</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>لواء غزة</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>data/photos\862.jpg</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>data/frames\862_28.jpg;data/frames\862_30.jpg;data/frames\862_32.jpg</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2026-05-12 14:52</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/862</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>864</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>أسيد مازن الحاج سلامة</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>اسيد مازن الحاج سلامه</t>
+        </is>
+      </c>
+      <c r="D401" s="1" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="E401" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>قائدفصيل</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>كتيبة الزيتون</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>لواء غزة</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>data/photos\864.jpg</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>data/frames\864_28.jpg;data/frames\864_30.jpg;data/frames\864_32.jpg</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>2026-05-12 16:43</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/864</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>866</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>محمود خليل فرحات</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>محمود خليل فرحات</t>
+        </is>
+      </c>
+      <c r="D402" s="1" t="inlineStr">
+        <is>
+          <t>1992-07-04</t>
+        </is>
+      </c>
+      <c r="E402" s="1" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>كتيبة الرضوان</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>لواء غزة</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>data/photos\866.jpg</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>data/frames\866_28.jpg;data/frames\866_30.jpg;data/frames\866_32.jpg</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>2026-05-12 17:46</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/866</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>868</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>إيهاب عبد الرحيم حمادة</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>ايهاب عبد الرحيم حماده</t>
+        </is>
+      </c>
+      <c r="D403" s="1" t="inlineStr">
+        <is>
+          <t>1984-06-26</t>
+        </is>
+      </c>
+      <c r="E403" s="1" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>قائدسرية</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>كتيبة التفاح والدرج</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>لواء غزة</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>data/photos\868.jpg</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>data/frames\868_28.jpg;data/frames\868_30.jpg;data/frames\868_32.jpg</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:51</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/868</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>870</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>أحمد عبد العزيز التلباني</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>احمد عبد العزيز التلباني</t>
+        </is>
+      </c>
+      <c r="D404" s="1" t="inlineStr">
+        <is>
+          <t>1986-04-07</t>
+        </is>
+      </c>
+      <c r="E404" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>كتيبة حطين</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>لواء الوسطى</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>data/photos\870.jpg</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>data/frames\870_28.jpg;data/frames\870_30.jpg;data/frames\870_32.jpg</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2026-05-13 07:01</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/870</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>872</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>أحمد سعيد الشيخ علي</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>احمد سعيد الشيخ علي</t>
+        </is>
+      </c>
+      <c r="D405" s="1" t="inlineStr">
+        <is>
+          <t>1988-07-15</t>
+        </is>
+      </c>
+      <c r="E405" s="1" t="inlineStr">
+        <is>
+          <t>2023-12-24</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>كتيبة حطين</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>لواء الوسطى</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>data/photos\872.jpg</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>data/frames\872_28.jpg;data/frames\872_30.jpg;data/frames\872_32.jpg</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>2026-05-13 09:38</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/872</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>874</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>غالب عبد الرحمن أبو شاويش</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>غالب عبد الرحمن ابو شاويش</t>
+        </is>
+      </c>
+      <c r="D406" s="1" t="inlineStr">
+        <is>
+          <t>1974-05-22 ٥ا تاريحخ الشهادة 11-22 2025</t>
+        </is>
+      </c>
+      <c r="E406" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>قائسد سرية</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>كتيبة القدس</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>لواء الوسطى</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>data/photos\874.jpg</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>data/frames\874_28.jpg;data/frames\874_30.jpg;data/frames\874_32.jpg</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2026-05-13 10:58</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/874</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>876</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>خالد أحمد مسمح "أبو أحمد"</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>خالد احمد مسمح "ابو احمد"</t>
+        </is>
+      </c>
+      <c r="D407" s="1" t="inlineStr">
+        <is>
+          <t>1974-11-17</t>
+        </is>
+      </c>
+      <c r="E407" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>قائد كتيبة</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>كتيبة حطين</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>لواء الوسطى</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>data/photos\876.jpg</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>data/frames\876_28.jpg;data/frames\876_30.jpg;data/frames\876_32.jpg</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:27</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/876</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>878</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>محمد غالب عثمان</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>محمد غالب عثمان</t>
+        </is>
+      </c>
+      <c r="D408" s="1" t="inlineStr">
+        <is>
+          <t>1977-05-07</t>
+        </is>
+      </c>
+      <c r="E408" s="1" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>قائسد مجموعة</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>كتيبة القدس</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>لواء الوسطى</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>data/photos\878.jpg</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>data/frames\878_28.jpg;data/frames\878_30.jpg;data/frames\878_32.jpg</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:48</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/878</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>partial_martyrdom</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>880</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>سامي عدنان  الشامي</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>سامي عدنان الشامي</t>
+        </is>
+      </c>
+      <c r="D409" s="1" t="inlineStr">
+        <is>
+          <t>1984-09-08</t>
+        </is>
+      </c>
+      <c r="E409" s="1" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>قائسد فصيل</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>كتيبة القدس</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>لواء الوسطى</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>data/photos\880.jpg</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>data/frames\880_28.jpg;data/frames\880_30.jpg;data/frames\880_32.jpg</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-05-13 17:01</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/880</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>partial_martyrdom</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>882</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>يامن خليل أبو طير</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>يامن خليل ابو طير</t>
+        </is>
+      </c>
+      <c r="D410" s="1" t="inlineStr">
+        <is>
+          <t>1978-05-20</t>
+        </is>
+      </c>
+      <c r="E410" s="1" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>مجاهد _ قسامي</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>كتيبة الصحابي أسد الله حمزة</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>لواء خانيونس</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>data/photos\882.jpg</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>data/frames\882_28.jpg;data/frames\882_30.jpg;data/frames\882_32.jpg</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-05-13 18:39</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/882</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>884</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>محمد محمود الأسطل</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>محمد محمود الاسطل</t>
+        </is>
+      </c>
+      <c r="D411" s="1" t="inlineStr">
+        <is>
+          <t>2002-12-31</t>
+        </is>
+      </c>
+      <c r="E411" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>مجاهد قسا م</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>كتيبة الصحابي أسامة بن زيد</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>لواء خانيونس</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>data/photos\884.jpg</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>data/frames\884_28.jpg;data/frames\884_30.jpg;data/frames\884_32.jpg</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2026-05-13 19:31</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/884</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>887</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>حسن علي حسونة</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>حسن علي حسونه</t>
+        </is>
+      </c>
+      <c r="D412" s="1" t="inlineStr">
+        <is>
+          <t>1986-07-24</t>
+        </is>
+      </c>
+      <c r="E412" s="1" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد محمد أبو شمالة</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>لواء رفح</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>data/photos\887.jpg</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>data/frames\887_28.jpg;data/frames\887_30.jpg;data/frames\887_32.jpg</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-05-14 07:01</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/887</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>889</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>محمد حامد أبو شعر</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>محمد حامد ابو شعر</t>
+        </is>
+      </c>
+      <c r="D413" s="1" t="inlineStr">
+        <is>
+          <t>2004-04-07</t>
+        </is>
+      </c>
+      <c r="E413" s="1" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>مجاهد قسا م</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد محمد أبو حرب</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>لواء رفح</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>data/photos\889.jpg</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>data/frames\889_28.jpg;data/frames\889_30.jpg;data/frames\889_32.jpg</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-05-14 09:14</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/889</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>891</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>أحمد توفيق أبو رتيمة</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>احمد توفيق ابو رتيمه</t>
+        </is>
+      </c>
+      <c r="D414" s="1" t="inlineStr">
+        <is>
+          <t>1989-05-03</t>
+        </is>
+      </c>
+      <c r="E414" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد محمد الشمالي</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>لواء رفح</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>data/photos\891.jpg</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>data/frames\891_28.jpg;data/frames\891_30.jpg;data/frames\891_32.jpg</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-05-14 10:59</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/891</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>893</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>وسام عبد الله أحمد</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>وسام عبد الله احمد</t>
+        </is>
+      </c>
+      <c r="D415" s="1" t="inlineStr">
+        <is>
+          <t>1992-08-07</t>
+        </is>
+      </c>
+      <c r="E415" s="1" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد رائد العطار</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>لواء رفح</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>data/photos\893.jpg</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>data/frames\893_28.jpg;data/frames\893_30.jpg;data/frames\893_32.jpg</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2026-05-14 13:24</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/893</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>895</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>طارق أحمد أبو يونس</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>طارق احمد ابو يونس</t>
+        </is>
+      </c>
+      <c r="D416" s="1" t="inlineStr">
+        <is>
+          <t>1986-10-26</t>
+        </is>
+      </c>
+      <c r="E416" s="1" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>مجاهد قسا مر</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>كتيبة المدفعية</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>لواء رفح</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>data/photos\895.jpg</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>data/frames\895_28.jpg;data/frames\895_30.jpg;data/frames\895_32.jpg</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>2026-05-14 15:17</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/895</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>897</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>زارع سامي البليشي</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>زارع سامي البليشي</t>
+        </is>
+      </c>
+      <c r="D417" s="1" t="inlineStr">
+        <is>
+          <t>1992-07-17</t>
+        </is>
+      </c>
+      <c r="E417" s="1" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد محمد أبو شمالة</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>لواء رفح</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>data/photos\897.jpg</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>data/frames\897_28.jpg;data/frames\897_30.jpg;data/frames\897_32.jpg</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>2026-05-14 15:17</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/897</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>899</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>محمد فايز برهوم</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>محمد فايز برهوم</t>
+        </is>
+      </c>
+      <c r="D418" s="1" t="inlineStr">
+        <is>
+          <t>1985-08-14</t>
+        </is>
+      </c>
+      <c r="E418" s="1" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>قائسد سريسة</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>لواء رفح</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>data/photos\899.jpg</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>data/frames\899_28.jpg;data/frames\899_30.jpg;data/frames\899_32.jpg</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2026-05-14 17:05</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/899</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>901</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>عبد الرحمن محمد أبو السعود</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>عبد الرحمن محمد ابو السعود</t>
+        </is>
+      </c>
+      <c r="D419" s="1" t="inlineStr">
+        <is>
+          <t>1999-01-08</t>
+        </is>
+      </c>
+      <c r="E419" s="1" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>مجاهد قسا مي</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد محمد أبو شمالة</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>لواء رفح</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>data/photos\901.jpg</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>data/frames\901_28.jpg;data/frames\901_30.jpg;data/frames\901_32.jpg</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:58</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/901</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>903</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>محمد عبد الرحمن شهاب</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>محمد عبد الرحمن شهاب</t>
+        </is>
+      </c>
+      <c r="D420" s="1" t="inlineStr">
+        <is>
+          <t>1986-04-22</t>
+        </is>
+      </c>
+      <c r="E420" s="1" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>نائب قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد عبد الرؤوف نبهان</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>لواء الشمال</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>data/photos\903.jpg</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>data/frames\903_28.jpg;data/frames\903_30.jpg;data/frames\903_32.jpg</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2026-05-16 07:02</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/903</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>905</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>سليمان محمد صلاح</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>سليمان محمد صلاح</t>
+        </is>
+      </c>
+      <c r="D421" s="1" t="inlineStr">
+        <is>
+          <t>1991-12-03</t>
+        </is>
+      </c>
+      <c r="E421" s="1" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد فوزي أبو القرع</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>لواء الشمال</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>data/photos\905.jpg</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>data/frames\905_28.jpg;data/frames\905_30.jpg;data/frames\905_32.jpg</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>2026-05-16 10:27</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/905</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>907</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>محمد خميس حمودة</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>محمد خميس حموده</t>
+        </is>
+      </c>
+      <c r="D422" s="1" t="inlineStr">
+        <is>
+          <t>1987-08-24</t>
+        </is>
+      </c>
+      <c r="E422" s="1" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>قائسد سرية</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>كتيبة بيت لاهيا</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>لواء الشمال</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>data/photos\907.jpg</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>data/frames\907_28.jpg;data/frames\907_30.jpg;data/frames\907_32.jpg</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>2026-05-16 12:02</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/907</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>909</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>إبراهيم ناهض الشنباري</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>ابراهيم ناهض الشنباري</t>
+        </is>
+      </c>
+      <c r="D423" s="1" t="inlineStr">
+        <is>
+          <t>1989-09-27</t>
+        </is>
+      </c>
+      <c r="E423" s="1" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>نائب قائد فصيل</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد نضال ناصر</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>لواء الشمال</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>data/photos\909.jpg</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>data/frames\909_28.jpg;data/frames\909_30.jpg;data/frames\909_32.jpg</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>2026-05-16 13:30</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/909</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>911</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>محمد فتحي لبد</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>محمد فتحي لبد</t>
+        </is>
+      </c>
+      <c r="D424" s="1" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="E424" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>قائد سرية</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد عماد عقل</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>لواء الشمال</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>data/photos\911.jpg</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>data/frames\911_28.jpg;data/frames\911_30.jpg;data/frames\911_32.jpg</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>2026-05-16 15:05</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/911</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>913</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>نضال محمد شعبان</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>نضال محمد شعبان</t>
+        </is>
+      </c>
+      <c r="D425" s="1" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="E425" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>قائد مجموعة</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد عماد عقل</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>لواء الشمال</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>data/photos\913.jpg</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>data/frames\913_28.jpg;data/frames\913_30.jpg;data/frames\913_32.jpg</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>2026-05-16 16:36</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/913</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>915</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>أحمد حمدي الشلفوح</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>احمد حمدي الشلفوح</t>
+        </is>
+      </c>
+      <c r="D426" s="1" t="inlineStr"/>
+      <c r="E426" s="1" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>قائسد فصيل</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد سهيل زيادة</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>لواء الشمال</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>data/photos\915.jpg</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>data/frames\915_28.jpg;data/frames\915_30.jpg;data/frames\915_32.jpg</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>2026-05-16 18:27</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/915</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>partial_birth</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
         <is>
           <t>unique</t>
         </is>

--- a/data/martyrs.xlsx
+++ b/data/martyrs.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P426"/>
+  <dimension ref="A1:P428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27044,13 +27044,11 @@
           <t>2023-11-01</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr">
         <is>
           <t>نائب قائد مجموعة</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -27116,13 +27114,11 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr">
         <is>
           <t>مجاهد قسا مو</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -27188,13 +27184,11 @@
           <t>2024-03-24</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr">
         <is>
           <t>مجاهد قسا مو</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -27256,13 +27250,11 @@
           <t>2023-12-03</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr">
         <is>
           <t>قائد مجموعة</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -27328,13 +27320,11 @@
           <t>2024-02-03</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr">
         <is>
           <t>مجاهد قسا مو</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -27400,13 +27390,11 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr">
         <is>
           <t>قائدسرية</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr">
         <is>
           <t>كتيبة التفاح والدرج</t>
@@ -27472,13 +27460,11 @@
           <t>2023-12-15</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr"/>
       <c r="G397" t="inlineStr">
         <is>
           <t>قائد مجموعة</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr">
         <is>
           <t>كتيبة الرضوان</t>
@@ -27544,13 +27530,11 @@
           <t>2023-12-07</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr">
         <is>
           <t>قائدفصيل</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr">
         <is>
           <t>كتيبة الشجاعية</t>
@@ -27616,13 +27600,11 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr">
         <is>
           <t>قائد فصيل</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr">
         <is>
           <t>كتيبة الرضوان</t>
@@ -27688,13 +27670,11 @@
           <t>2023-12-07</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
           <t>نائب قائد كتيبة</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr">
         <is>
           <t>كتيبة الشجاعية</t>
@@ -27760,13 +27740,11 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr">
         <is>
           <t>قائدفصيل</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr">
         <is>
           <t>كتيبة الزيتون</t>
@@ -27832,13 +27810,11 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr">
         <is>
           <t>قائد فصيل</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr">
         <is>
           <t>كتيبة الرضوان</t>
@@ -27904,13 +27880,11 @@
           <t>29</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr">
         <is>
           <t>قائدسرية</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr">
         <is>
           <t>كتيبة التفاح والدرج</t>
@@ -27976,13 +27950,11 @@
           <t>2024-10-17</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr">
         <is>
           <t>قائد فصيل</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr">
         <is>
           <t>كتيبة حطين</t>
@@ -28048,13 +28020,11 @@
           <t>2023-12-24</t>
         </is>
       </c>
-      <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr">
         <is>
           <t>قائد فصيل</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr">
         <is>
           <t>كتيبة حطين</t>
@@ -28192,13 +28162,11 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="F407" t="inlineStr"/>
       <c r="G407" t="inlineStr">
         <is>
           <t>قائد كتيبة</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr">
         <is>
           <t>كتيبة حطين</t>
@@ -28260,13 +28228,11 @@
         </is>
       </c>
       <c r="E408" s="1" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr">
         <is>
           <t>قائسد مجموعة</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr">
         <is>
           <t>كتيبة القدس</t>
@@ -28328,13 +28294,11 @@
         </is>
       </c>
       <c r="E409" s="1" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr">
         <is>
           <t>قائسد فصيل</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr">
         <is>
           <t>كتيبة القدس</t>
@@ -28400,13 +28364,11 @@
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
           <t>مجاهد _ قسامي</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr">
         <is>
           <t>كتيبة الصحابي أسد الله حمزة</t>
@@ -28472,13 +28434,11 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr">
         <is>
           <t>مجاهد قسا م</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr">
         <is>
           <t>كتيبة الصحابي أسامة بن زيد</t>
@@ -28544,13 +28504,11 @@
           <t>2023-10-19</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
           <t>قائد فصيل</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو شمالة</t>
@@ -28616,13 +28574,11 @@
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr">
         <is>
           <t>مجاهد قسا م</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو حرب</t>
@@ -28688,13 +28644,11 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
           <t>قائد فصيل</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد الشمالي</t>
@@ -28760,13 +28714,11 @@
           <t>2024-06-09</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr">
         <is>
           <t>قائد فصيل</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr">
         <is>
           <t>كتيبة الشهيد رائد العطار</t>
@@ -28832,13 +28784,11 @@
           <t>2023-10-29</t>
         </is>
       </c>
-      <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
           <t>مجاهد قسا مر</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr">
         <is>
           <t>كتيبة المدفعية</t>
@@ -28904,13 +28854,11 @@
           <t>2024-05-29</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
       <c r="G417" t="inlineStr">
         <is>
           <t>قائد فصيل</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو شمالة</t>
@@ -28976,14 +28924,11 @@
           <t>2023-11-23</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr">
         <is>
           <t>قائسد سريسة</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr"/>
-      <c r="I418" t="inlineStr"/>
       <c r="J418" t="inlineStr">
         <is>
           <t>لواء رفح</t>
@@ -29044,13 +28989,11 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr">
         <is>
           <t>مجاهد قسا مي</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr"/>
       <c r="I419" t="inlineStr">
         <is>
           <t>كتيبة الشهيد محمد أبو شمالة</t>
@@ -29116,13 +29059,11 @@
           <t>2023-10-13</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
           <t>نائب قائد فصيل</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr"/>
       <c r="I420" t="inlineStr">
         <is>
           <t>كتيبة الشهيد عبد الرؤوف نبهان</t>
@@ -29188,13 +29129,11 @@
           <t>2023-10-09</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
           <t>قائد فصيل</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr"/>
       <c r="I421" t="inlineStr">
         <is>
           <t>كتيبة الشهيد فوزي أبو القرع</t>
@@ -29260,13 +29199,11 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="F422" t="inlineStr"/>
       <c r="G422" t="inlineStr">
         <is>
           <t>قائسد سرية</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr"/>
       <c r="I422" t="inlineStr">
         <is>
           <t>كتيبة بيت لاهيا</t>
@@ -29332,13 +29269,11 @@
           <t>2023-10-10</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr">
         <is>
           <t>نائب قائد فصيل</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr"/>
       <c r="I423" t="inlineStr">
         <is>
           <t>كتيبة الشهيد نضال ناصر</t>
@@ -29404,13 +29339,11 @@
           <t>2025-06-20</t>
         </is>
       </c>
-      <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr">
         <is>
           <t>قائد سرية</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr"/>
       <c r="I424" t="inlineStr">
         <is>
           <t>كتيبة الشهيد عماد عقل</t>
@@ -29476,13 +29409,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr">
         <is>
           <t>قائد مجموعة</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr"/>
       <c r="I425" t="inlineStr">
         <is>
           <t>كتيبة الشهيد عماد عقل</t>
@@ -29544,13 +29475,11 @@
           <t>2024-05-24</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
           <t>قائسد فصيل</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr"/>
       <c r="I426" t="inlineStr">
         <is>
           <t>كتيبة الشهيد سهيل زيادة</t>
@@ -29587,6 +29516,146 @@
         </is>
       </c>
       <c r="P426" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>922</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>بلال محمد جودة</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>بلال محمد جوده</t>
+        </is>
+      </c>
+      <c r="D427" s="1" t="inlineStr">
+        <is>
+          <t>1987-02-15</t>
+        </is>
+      </c>
+      <c r="E427" s="1" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>قائد سرية</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>كتيبة الشهيد عبد الرؤوف نبهان</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>لواء الشمال</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>data/photos\922.jpg</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>data/frames\922_28.jpg;data/frames\922_30.jpg;data/frames\922_32.jpg</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>2026-05-16 20:01</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/922</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>924</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>خالد علي عبد الرحمن</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>خالد علي عبد الرحمن</t>
+        </is>
+      </c>
+      <c r="D428" s="1" t="inlineStr">
+        <is>
+          <t>1962-01-08</t>
+        </is>
+      </c>
+      <c r="E428" s="1" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>قائد فصيل</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>كتيبة حطين</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>لواء الوسطى</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>data/photos\924.jpg</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>data/frames\924_28.jpg;data/frames\924_30.jpg;data/frames\924_32.jpg</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2026-05-17 07:03</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>https://t.me/AqmarTofan/924</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
         <is>
           <t>unique</t>
         </is>
